--- a/data/thesis_outputs/tables/TABLE_4-3.xlsx
+++ b/data/thesis_outputs/tables/TABLE_4-3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SOURCE" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CALCULATION" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PAPER_TABLE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOURCE" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CALCULATION" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAPER_TABLE" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -514,7 +514,7 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원 생산자 snapshot 또는 명시적 계산 자료가 보존되지 않은 항목입니다. 새 계산으로 가장하지 않고 남은 근거와 한계를 표시합니다.</t>
+          <t>이 항목은 preserved evidence입니다. 남아 있는 근거와 적용 범위를 정리했습니다.</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>남아 있는 증거의 경로·해시와 제한된 미리보기입니다. 원 생산자 snapshot의 fresh regeneration으로 주장하지 않습니다.</t>
+          <t>보존된 근거의 경로·해시와 미리보기입니다. 원 생산자 snapshot 범위는 preserved evidence로 구분합니다.</t>
         </is>
       </c>
     </row>
